--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>69.05</v>
+        <v>690.46</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45.9</v>
+        <v>459.03</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.5</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32.93</v>
+        <v>329.28</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.4</v>
+        <v>274.03</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25.22</v>
+        <v>252.24</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>22.95</v>
+        <v>229.51</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>22.59</v>
+        <v>225.9</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>21.89</v>
+        <v>218.87</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21.79</v>
+        <v>217.85</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20.87</v>
+        <v>208.68</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>20.7</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20.08</v>
+        <v>200.79</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>18.97</v>
+        <v>189.71</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>18.89</v>
+        <v>188.87</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>18.31</v>
+        <v>183.12</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>18.22</v>
+        <v>182.22</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17.44</v>
+        <v>174.4</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16.8</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>15.57</v>
+        <v>155.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -39,7 +39,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-04 07:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:57</t>
+    <t xml:space="preserve">2026-10-05 07:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
